--- a/Overall_Rebate_Efficiency.xlsx
+++ b/Overall_Rebate_Efficiency.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john.tan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cogentholdings-my.sharepoint.com/personal/john_tan_sh-cogent_com_sg/Documents/Documents/Linda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144207D7-6374-4C0F-900D-F7C21F8239A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{38B7C5C2-BCDD-4727-BBED-9A6509AFB655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9C88EA7-9DFB-4E29-911B-6A682D8F8495}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{C0E73409-90F9-4F3A-A281-E5B658230860}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="OverallRebateEfficiency" sheetId="1" r:id="rId1"/>
     <sheet name="PSA_LOLO" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Week_2</t>
   </si>
@@ -108,10 +108,10 @@
     <t>Week_24</t>
   </si>
   <si>
-    <t>Efficiency</t>
-  </si>
-  <si>
-    <t>Week</t>
+    <t>psa_lolo_20</t>
+  </si>
+  <si>
+    <t>psa_lolo_40</t>
   </si>
   <si>
     <t>Week_25</t>
@@ -132,9 +132,6 @@
     <t>Week_30</t>
   </si>
   <si>
-    <t>PSALOLO</t>
-  </si>
-  <si>
     <t>Week_31</t>
   </si>
   <si>
@@ -148,13 +145,28 @@
   </si>
   <si>
     <t>Week_35</t>
+  </si>
+  <si>
+    <t>Week_36</t>
+  </si>
+  <si>
+    <t>Week_37</t>
+  </si>
+  <si>
+    <t>Week_38</t>
+  </si>
+  <si>
+    <t>Week_39</t>
+  </si>
+  <si>
+    <t>Week_40</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -534,341 +546,294 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B8068D1-8FEE-4DE6-A49E-26630330CB1A}">
-  <dimension ref="A1:AB35"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:AM2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="7.25" style="1" customWidth="1"/>
-    <col min="4" max="5" width="7.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.625" style="1" customWidth="1"/>
-    <col min="10" max="11" width="7.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="7.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="7.42578125" style="1" customWidth="1"/>
     <col min="12" max="14" width="8" style="1" customWidth="1"/>
-    <col min="15" max="16" width="7.75" style="1" customWidth="1"/>
+    <col min="15" max="16" width="7.7109375" style="1" customWidth="1"/>
     <col min="17" max="17" width="8" style="1" customWidth="1"/>
-    <col min="18" max="18" width="7.875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="7.625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.75" style="1" customWidth="1"/>
+    <col min="18" max="18" width="7.85546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.5703125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.7109375" style="1" customWidth="1"/>
     <col min="21" max="21" width="8" style="1" customWidth="1"/>
-    <col min="22" max="22" width="8.375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="7.875" style="1" customWidth="1"/>
-    <col min="24" max="28" width="9.125" style="1"/>
+    <col min="22" max="22" width="8.42578125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="7.85546875" style="1" customWidth="1"/>
+    <col min="24" max="28" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>0.81902758125101194</v>
       </c>
       <c r="B2" s="2">
-        <v>0.81902758125101194</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2">
         <v>0.70771875002575046</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="C2" s="2">
         <v>0.8143757256676234</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="D2" s="2">
         <v>0.86329223749621598</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="E2" s="2">
         <v>0.72271733584093245</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="F2" s="2">
         <v>0.80045199754182117</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="G2" s="2">
         <v>0.81658725255829046</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="H2" s="2">
         <v>0.70407064079442705</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="I2" s="2">
         <v>0.78973223209760735</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="J2" s="2">
         <v>0.66839334250536941</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="K2" s="2">
         <v>0.76042716356387874</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="L2" s="2">
         <v>0.75134139587460569</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="M2" s="2">
         <v>0.76090901606098194</v>
       </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="N2" s="2">
         <v>0.78745377698122987</v>
       </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2">
+      <c r="O2" s="2">
         <v>0.783496890761745</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="P2" s="2">
         <v>0.78504855531571338</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2">
+      <c r="Q2" s="2">
         <v>0.72604132280915179</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="R2" s="2">
         <v>0.70779427717954235</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="2">
+      <c r="S2" s="2">
         <v>0.72415889219129936</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="2">
+      <c r="T2" s="2">
         <v>0.74929222590181954</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2">
+      <c r="U2" s="2">
         <v>0.81663576787600167</v>
       </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="2">
+      <c r="V2" s="2">
         <v>0.77481098477947863</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="2">
+      <c r="W2" s="2">
         <v>0.68286799137297094</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0.71750000000000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1">
-        <v>0.75770000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="1">
-        <v>0.71870000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="1">
-        <v>0.72430000000000005</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="1">
-        <v>0.72189999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="1">
-        <v>0.77210000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0.73399999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="1">
+      <c r="X2" s="1">
+        <v>0.71753620202535084</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>0.75770383515166584</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>0.71872284191200064</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>0.72426771148081248</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>0.72190382509172002</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>0.77214239490772107</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>0.73470000000000002</v>
+      </c>
+      <c r="AE2" s="1">
         <v>0.86199999999999999</v>
       </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0.80400000000000005</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0.7631</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="1">
+      <c r="AF2" s="1">
+        <v>0.80410000000000004</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>0.76910000000000001</v>
+      </c>
+      <c r="AH2" s="1">
         <v>0.78369999999999995</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>0.79510000000000003</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>0.84079999999999999</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>0.73909999999999998</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>0.79239999999999999</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>0.77449999999999997</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F588B96-5F90-4A9C-998D-1582689D455F}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1"/>
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>20</v>
+        <v>38763</v>
       </c>
       <c r="B2">
-        <v>32214</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>40</v>
-      </c>
-      <c r="B3">
-        <v>8142</v>
+        <v>13629</v>
       </c>
     </row>
   </sheetData>

--- a/Overall_Rebate_Efficiency.xlsx
+++ b/Overall_Rebate_Efficiency.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cogentholdings-my.sharepoint.com/personal/john_tan_sh-cogent_com_sg/Documents/Documents/Linda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{38B7C5C2-BCDD-4727-BBED-9A6509AFB655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9C88EA7-9DFB-4E29-911B-6A682D8F8495}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{38B7C5C2-BCDD-4727-BBED-9A6509AFB655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F079424C-3048-4A1F-ADA2-9D170E7232CA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{C0E73409-90F9-4F3A-A281-E5B658230860}"/>
+    <workbookView xWindow="21030" yWindow="135" windowWidth="24045" windowHeight="14565" xr2:uid="{C0E73409-90F9-4F3A-A281-E5B658230860}"/>
   </bookViews>
   <sheets>
     <sheet name="OverallRebateEfficiency" sheetId="1" r:id="rId1"/>
-    <sheet name="PSA_LOLO" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="PSA_LOLO" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="42">
   <si>
     <t>Week_2</t>
   </si>
@@ -160,6 +162,9 @@
   </si>
   <si>
     <t>Week_40</t>
+  </si>
+  <si>
+    <t>Week</t>
   </si>
 </sst>
 </file>
@@ -546,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B8068D1-8FEE-4DE6-A49E-26630330CB1A}">
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AM54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" customWidth="1"/>
@@ -571,242 +576,421 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+    </row>
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="2">
+        <v>0.81902758125101194</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+    </row>
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B3" s="2">
+        <v>0.70771875002575046</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B4" s="2">
+        <v>0.8143757256676234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B5" s="2">
+        <v>0.86329223749621598</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B6" s="2">
+        <v>0.72271733584093245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B7" s="2">
+        <v>0.80045199754182117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B8" s="2">
+        <v>0.81658725255829046</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="B9" s="2">
+        <v>0.70407064079442705</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B10" s="2">
+        <v>0.78973223209760735</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B11" s="2">
+        <v>0.66839334250536941</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="B12" s="2">
+        <v>0.76042716356387874</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="B13" s="2">
+        <v>0.75134139587460569</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="B14" s="2">
+        <v>0.76090901606098194</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="B15" s="2">
+        <v>0.78745377698122987</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="B16" s="2">
+        <v>0.783496890761745</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="B17" s="2">
+        <v>0.78504855531571338</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="B18" s="2">
+        <v>0.72604132280915179</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="B19" s="2">
+        <v>0.70779427717954235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="B20" s="2">
+        <v>0.72415889219129936</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="B21" s="2">
+        <v>0.74929222590181954</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="B22" s="2">
+        <v>0.81663576787600167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="B23" s="2">
+        <v>0.77481098477947863</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="B24" s="2">
+        <v>0.68286799137297094</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="B25" s="1">
+        <v>0.71753620202535084</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="B26" s="1">
+        <v>0.75770383515166584</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="B27" s="1">
+        <v>0.71872284191200064</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="B28" s="1">
+        <v>0.72426771148081248</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="B29" s="1">
+        <v>0.72190382509172002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="B30" s="1">
+        <v>0.77214239490772107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="B31" s="1">
+        <v>0.73470000000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="B32" s="1">
+        <v>0.86199999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="B33" s="1">
+        <v>0.80410000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="B34" s="1">
+        <v>0.76910000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="B35" s="1">
+        <v>0.78369999999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="B36" s="1">
+        <v>0.79510000000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="B37" s="1">
+        <v>0.84079999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="B38" s="1">
+        <v>0.73909999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="B39" s="1">
+        <v>0.79239999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>0.81902758125101194</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0.70771875002575046</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.8143757256676234</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.86329223749621598</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.72271733584093245</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0.80045199754182117</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.81658725255829046</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0.70407064079442705</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0.78973223209760735</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.66839334250536941</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0.76042716356387874</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0.75134139587460569</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0.76090901606098194</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0.78745377698122987</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0.783496890761745</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0.78504855531571338</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>0.72604132280915179</v>
-      </c>
-      <c r="R2" s="2">
-        <v>0.70779427717954235</v>
-      </c>
-      <c r="S2" s="2">
-        <v>0.72415889219129936</v>
-      </c>
-      <c r="T2" s="2">
-        <v>0.74929222590181954</v>
-      </c>
-      <c r="U2" s="2">
-        <v>0.81663576787600167</v>
-      </c>
-      <c r="V2" s="2">
-        <v>0.77481098477947863</v>
-      </c>
-      <c r="W2" s="2">
-        <v>0.68286799137297094</v>
-      </c>
-      <c r="X2" s="1">
-        <v>0.71753620202535084</v>
-      </c>
-      <c r="Y2" s="1">
-        <v>0.75770383515166584</v>
-      </c>
-      <c r="Z2" s="1">
-        <v>0.71872284191200064</v>
-      </c>
-      <c r="AA2" s="1">
-        <v>0.72426771148081248</v>
-      </c>
-      <c r="AB2" s="1">
-        <v>0.72190382509172002</v>
-      </c>
-      <c r="AC2" s="1">
-        <v>0.77214239490772107</v>
-      </c>
-      <c r="AD2" s="1">
-        <v>0.73470000000000002</v>
-      </c>
-      <c r="AE2" s="1">
-        <v>0.86199999999999999</v>
-      </c>
-      <c r="AF2" s="1">
-        <v>0.80410000000000004</v>
-      </c>
-      <c r="AG2" s="1">
-        <v>0.76910000000000001</v>
-      </c>
-      <c r="AH2" s="1">
-        <v>0.78369999999999995</v>
-      </c>
-      <c r="AI2" s="1">
-        <v>0.79510000000000003</v>
-      </c>
-      <c r="AJ2" s="1">
-        <v>0.84079999999999999</v>
-      </c>
-      <c r="AK2" s="1">
-        <v>0.73909999999999998</v>
-      </c>
-      <c r="AL2" s="1">
-        <v>0.79239999999999999</v>
-      </c>
-      <c r="AM2" s="1">
+      <c r="B40" s="1">
         <v>0.77449999999999997</v>
       </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41"/>
+      <c r="B41"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42"/>
+      <c r="B42"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43"/>
+      <c r="B43"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44"/>
+      <c r="B44"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45"/>
+      <c r="B45"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46"/>
+      <c r="B46"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47"/>
+      <c r="B47"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48"/>
+      <c r="B48"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49"/>
+      <c r="B49"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50"/>
+      <c r="B50"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51"/>
+      <c r="B51"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52"/>
+      <c r="B52"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53"/>
+      <c r="B53"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54"/>
+      <c r="B54"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -816,6 +1000,581 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50079CCB-7DC8-40D8-9E20-61D5762311BF}">
+  <dimension ref="A1:AM2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>0.81902758125101194</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.70771875002575046</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.8143757256676234</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.86329223749621598</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.72271733584093245</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.80045199754182117</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.81658725255829046</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.70407064079442705</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.78973223209760735</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.66839334250536941</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.76042716356387874</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0.75134139587460569</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0.76090901606098194</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0.78745377698122987</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.783496890761745</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.78504855531571338</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0.72604132280915179</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0.70779427717954235</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0.72415889219129936</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0.74929222590181954</v>
+      </c>
+      <c r="U2" s="2">
+        <v>0.81663576787600167</v>
+      </c>
+      <c r="V2" s="2">
+        <v>0.77481098477947863</v>
+      </c>
+      <c r="W2" s="2">
+        <v>0.68286799137297094</v>
+      </c>
+      <c r="X2" s="1">
+        <v>0.71753620202535084</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>0.75770383515166584</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>0.71872284191200064</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>0.72426771148081248</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>0.72190382509172002</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>0.77214239490772107</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>0.73470000000000002</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>0.80410000000000004</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>0.76910000000000001</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>0.78369999999999995</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>0.79510000000000003</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>0.84079999999999999</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>0.73909999999999998</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>0.79239999999999999</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>0.77449999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BC41BD-5E02-4311-A0D5-BFE5406E0A5C}">
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.81902758125101194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.70771875002575046</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.8143757256676234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.86329223749621598</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.72271733584093245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.80045199754182117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.81658725255829046</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.70407064079442705</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.78973223209760735</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.66839334250536941</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.76042716356387874</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.75134139587460569</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.76090901606098194</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.78745377698122987</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.783496890761745</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.78504855531571338</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.72604132280915179</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.70779427717954235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.72415889219129936</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.74929222590181954</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.81663576787600167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.77481098477947863</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0.68286799137297094</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0.71753620202535084</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="1">
+        <v>0.75770383515166584</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1">
+        <v>0.71872284191200064</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1">
+        <v>0.72426771148081248</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1">
+        <v>0.72190382509172002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="1">
+        <v>0.77214239490772107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="1">
+        <v>0.73470000000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="1">
+        <v>0.86199999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="1">
+        <v>0.80410000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0.76910000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="1">
+        <v>0.78369999999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="1">
+        <v>0.79510000000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="1">
+        <v>0.84079999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0.73909999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="1">
+        <v>0.79239999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="1">
+        <v>0.77449999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F588B96-5F90-4A9C-998D-1582689D455F}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Overall_Rebate_Efficiency.xlsx
+++ b/Overall_Rebate_Efficiency.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cogentholdings-my.sharepoint.com/personal/john_tan_sh-cogent_com_sg/Documents/Documents/Linda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{38B7C5C2-BCDD-4727-BBED-9A6509AFB655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F079424C-3048-4A1F-ADA2-9D170E7232CA}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{38B7C5C2-BCDD-4727-BBED-9A6509AFB655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85A0145A-B053-407F-AFC9-FE2940B7D9CF}"/>
   <bookViews>
     <workbookView xWindow="21030" yWindow="135" windowWidth="24045" windowHeight="14565" xr2:uid="{C0E73409-90F9-4F3A-A281-E5B658230860}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="42">
   <si>
     <t>Week_2</t>
   </si>
@@ -576,365 +576,308 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
+      <c r="A2" s="2">
+        <v>0.81902758125101194</v>
       </c>
       <c r="B2" s="2">
-        <v>0.81902758125101194</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
-      <c r="AH2" s="1"/>
-      <c r="AI2" s="1"/>
-      <c r="AJ2" s="1"/>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="1"/>
-      <c r="AM2" s="1"/>
+        <v>0.70771875002575046</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.8143757256676234</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.86329223749621598</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.72271733584093245</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.80045199754182117</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.81658725255829046</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.70407064079442705</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.78973223209760735</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.66839334250536941</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0.76042716356387874</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0.75134139587460569</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0.76090901606098194</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0.78745377698122987</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.783496890761745</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.78504855531571338</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0.72604132280915179</v>
+      </c>
+      <c r="R2" s="2">
+        <v>0.70779427717954235</v>
+      </c>
+      <c r="S2" s="2">
+        <v>0.72415889219129936</v>
+      </c>
+      <c r="T2" s="2">
+        <v>0.74929222590181954</v>
+      </c>
+      <c r="U2" s="2">
+        <v>0.81663576787600167</v>
+      </c>
+      <c r="V2" s="2">
+        <v>0.77481098477947863</v>
+      </c>
+      <c r="W2" s="2">
+        <v>0.68286799137297094</v>
+      </c>
+      <c r="X2" s="1">
+        <v>0.71753620202535084</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>0.75770383515166584</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>0.71872284191200064</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>0.72426771148081248</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>0.72190382509172002</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>0.77214239490772107</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>0.73470000000000002</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>0.80410000000000004</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>0.76910000000000001</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>0.78369999999999995</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>0.79510000000000003</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>0.84079999999999999</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>0.73909999999999998</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>0.79239999999999999</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>0.77449999999999997</v>
+      </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.70771875002575046</v>
-      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.8143757256676234</v>
-      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0.86329223749621598</v>
-      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0.72271733584093245</v>
-      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0.80045199754182117</v>
-      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0.81658725255829046</v>
-      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0.70407064079442705</v>
-      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0.78973223209760735</v>
-      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0.66839334250536941</v>
-      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0.76042716356387874</v>
-      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0.75134139587460569</v>
-      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0.76090901606098194</v>
-      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2">
-        <v>0.78745377698122987</v>
-      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2">
-        <v>0.783496890761745</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2">
-        <v>0.78504855531571338</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2">
-        <v>0.72604132280915179</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="2">
-        <v>0.70779427717954235</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="2">
-        <v>0.72415889219129936</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="2">
-        <v>0.74929222590181954</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="2">
-        <v>0.81663576787600167</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="2">
-        <v>0.77481098477947863</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="2">
-        <v>0.68286799137297094</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0.71753620202535084</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1">
-        <v>0.75770383515166584</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="1">
-        <v>0.71872284191200064</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="1">
-        <v>0.72426771148081248</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="1">
-        <v>0.72190382509172002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="1">
-        <v>0.77214239490772107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="1">
-        <v>0.73470000000000002</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="1">
-        <v>0.86199999999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="1">
-        <v>0.80410000000000004</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0.76910000000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0.78369999999999995</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="1">
-        <v>0.79510000000000003</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="1">
-        <v>0.84079999999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="1">
-        <v>0.73909999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0.79239999999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="1">
-        <v>0.77449999999999997</v>
-      </c>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="2"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="2"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41"/>

--- a/Overall_Rebate_Efficiency.xlsx
+++ b/Overall_Rebate_Efficiency.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cogentholdings-my.sharepoint.com/personal/john_tan_sh-cogent_com_sg/Documents/Documents/Linda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{38B7C5C2-BCDD-4727-BBED-9A6509AFB655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85A0145A-B053-407F-AFC9-FE2940B7D9CF}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{38B7C5C2-BCDD-4727-BBED-9A6509AFB655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B91DD83-1D8F-4FEC-90EA-A60CB8F81848}"/>
   <bookViews>
     <workbookView xWindow="21030" yWindow="135" windowWidth="24045" windowHeight="14565" xr2:uid="{C0E73409-90F9-4F3A-A281-E5B658230860}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="42">
   <si>
     <t>Week_2</t>
   </si>
@@ -576,308 +576,365 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+    </row>
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="2">
+        <v>0.81902758125101194</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+    </row>
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B3" s="2">
+        <v>0.70771875002575046</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B4" s="2">
+        <v>0.8143757256676234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B5" s="2">
+        <v>0.86329223749621598</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B6" s="2">
+        <v>0.72271733584093245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B7" s="2">
+        <v>0.80045199754182117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B8" s="2">
+        <v>0.81658725255829046</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="B9" s="2">
+        <v>0.70407064079442705</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B10" s="2">
+        <v>0.78973223209760735</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B11" s="2">
+        <v>0.66839334250536941</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="B12" s="2">
+        <v>0.76042716356387874</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="B13" s="2">
+        <v>0.75134139587460569</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="B14" s="2">
+        <v>0.76090901606098194</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="B15" s="2">
+        <v>0.78745377698122987</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="B16" s="2">
+        <v>0.783496890761745</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="B17" s="2">
+        <v>0.78504855531571338</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="B18" s="2">
+        <v>0.72604132280915179</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="B19" s="2">
+        <v>0.70779427717954235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="B20" s="2">
+        <v>0.72415889219129936</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="B21" s="2">
+        <v>0.74929222590181954</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="B22" s="2">
+        <v>0.81663576787600167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="B23" s="2">
+        <v>0.77481098477947863</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="B24" s="2">
+        <v>0.68286799137297094</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="B25" s="1">
+        <v>0.71753620202535084</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="B26" s="1">
+        <v>0.75770383515166584</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="B27" s="1">
+        <v>0.71872284191200064</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="B28" s="1">
+        <v>0.72426771148081248</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="B29" s="1">
+        <v>0.72190382509172002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="B30" s="1">
+        <v>0.77214239490772107</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="B31" s="1">
+        <v>0.73470000000000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="B32" s="1">
+        <v>0.86199999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="B33" s="1">
+        <v>0.80410000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="B34" s="1">
+        <v>0.76910000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="B35" s="1">
+        <v>0.78369999999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="B36" s="1">
+        <v>0.79510000000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="B37" s="1">
+        <v>0.84079999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="B38" s="1">
+        <v>0.73909999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="B39" s="1">
+        <v>0.79239999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>0.81902758125101194</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0.70771875002575046</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.8143757256676234</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.86329223749621598</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0.72271733584093245</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0.80045199754182117</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.81658725255829046</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0.70407064079442705</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0.78973223209760735</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.66839334250536941</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0.76042716356387874</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0.75134139587460569</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0.76090901606098194</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0.78745377698122987</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0.783496890761745</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0.78504855531571338</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>0.72604132280915179</v>
-      </c>
-      <c r="R2" s="2">
-        <v>0.70779427717954235</v>
-      </c>
-      <c r="S2" s="2">
-        <v>0.72415889219129936</v>
-      </c>
-      <c r="T2" s="2">
-        <v>0.74929222590181954</v>
-      </c>
-      <c r="U2" s="2">
-        <v>0.81663576787600167</v>
-      </c>
-      <c r="V2" s="2">
-        <v>0.77481098477947863</v>
-      </c>
-      <c r="W2" s="2">
-        <v>0.68286799137297094</v>
-      </c>
-      <c r="X2" s="1">
-        <v>0.71753620202535084</v>
-      </c>
-      <c r="Y2" s="1">
-        <v>0.75770383515166584</v>
-      </c>
-      <c r="Z2" s="1">
-        <v>0.71872284191200064</v>
-      </c>
-      <c r="AA2" s="1">
-        <v>0.72426771148081248</v>
-      </c>
-      <c r="AB2" s="1">
-        <v>0.72190382509172002</v>
-      </c>
-      <c r="AC2" s="1">
-        <v>0.77214239490772107</v>
-      </c>
-      <c r="AD2" s="1">
-        <v>0.73470000000000002</v>
-      </c>
-      <c r="AE2" s="1">
-        <v>0.86199999999999999</v>
-      </c>
-      <c r="AF2" s="1">
-        <v>0.80410000000000004</v>
-      </c>
-      <c r="AG2" s="1">
-        <v>0.76910000000000001</v>
-      </c>
-      <c r="AH2" s="1">
-        <v>0.78369999999999995</v>
-      </c>
-      <c r="AI2" s="1">
-        <v>0.79510000000000003</v>
-      </c>
-      <c r="AJ2" s="1">
-        <v>0.84079999999999999</v>
-      </c>
-      <c r="AK2" s="1">
-        <v>0.73909999999999998</v>
-      </c>
-      <c r="AL2" s="1">
-        <v>0.79239999999999999</v>
-      </c>
-      <c r="AM2" s="1">
+      <c r="B40" s="1">
         <v>0.77449999999999997</v>
       </c>
-    </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="2"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41"/>

--- a/Overall_Rebate_Efficiency.xlsx
+++ b/Overall_Rebate_Efficiency.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cogentholdings-my.sharepoint.com/personal/john_tan_sh-cogent_com_sg/Documents/Documents/Linda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john.tan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="8_{38B7C5C2-BCDD-4727-BBED-9A6509AFB655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B91DD83-1D8F-4FEC-90EA-A60CB8F81848}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D4C562-A030-4EA2-AEE1-94F075A81618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21030" yWindow="135" windowWidth="24045" windowHeight="14565" xr2:uid="{C0E73409-90F9-4F3A-A281-E5B658230860}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C0E73409-90F9-4F3A-A281-E5B658230860}"/>
   </bookViews>
   <sheets>
     <sheet name="OverallRebateEfficiency" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="43">
   <si>
     <t>Week_2</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>Week</t>
+  </si>
+  <si>
+    <t>Week_41</t>
   </si>
 </sst>
 </file>
@@ -937,8 +940,12 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41"/>
-      <c r="B41"/>
+      <c r="A41" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="1">
+        <v>0.77159999999999995</v>
+      </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42"/>

--- a/Overall_Rebate_Efficiency.xlsx
+++ b/Overall_Rebate_Efficiency.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john.tan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D4C562-A030-4EA2-AEE1-94F075A81618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D395473-53A3-4D6C-888E-20C68749BEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C0E73409-90F9-4F3A-A281-E5B658230860}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="44">
   <si>
     <t>Week_2</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>Week_41</t>
+  </si>
+  <si>
+    <t>Efficiency</t>
   </si>
 </sst>
 </file>
@@ -582,7 +585,9 @@
       <c r="A1" t="s">
         <v>41</v>
       </c>
-      <c r="B1"/>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>

--- a/Overall_Rebate_Efficiency.xlsx
+++ b/Overall_Rebate_Efficiency.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\john.tan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D395473-53A3-4D6C-888E-20C68749BEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565CD772-C8EC-43CB-8A22-08014953A07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C0E73409-90F9-4F3A-A281-E5B658230860}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="43">
   <si>
     <t>Week_2</t>
   </si>
@@ -168,9 +168,6 @@
   </si>
   <si>
     <t>Week_41</t>
-  </si>
-  <si>
-    <t>Efficiency</t>
   </si>
 </sst>
 </file>
@@ -585,9 +582,7 @@
       <c r="A1" t="s">
         <v>41</v>
       </c>
-      <c r="B1" t="s">
-        <v>43</v>
-      </c>
+      <c r="B1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
